--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
@@ -8332,12 +8332,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>介護予防事業対象者数の分析</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -8355,22 +8355,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>56.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>-26.7</v>
+        <v>-21.4</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="16" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）</t>
+          <t>町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない。ワークシートに載る実施状況調査の回答も、従前相当の利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。町の控えとの突合が要る</t>
         </is>
       </c>
     </row>
@@ -8391,22 +8391,22 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>1-8</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>介護予防事業対象者数の分析</t>
+          <t>工程・協議会日程の合意と確認事項の照会</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -8419,22 +8419,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="I51" s="13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J51" s="13" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>-21.4</v>
+        <v>-16.4</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない。ワークシートに載る実施状況調査の回答も、従前相当の利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。町の控えとの突合が要る</t>
+          <t>町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない。最も厳しい案Aでも第1回の期限は11月6日で、残りは1か月である</t>
         </is>
       </c>
     </row>
@@ -8455,22 +8455,22 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>工程・協議会日程の合意と確認事項の照会</t>
+          <t>認知症高齢者の分析</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -8480,34 +8480,34 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I52" s="13" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>-16.4</v>
+        <v>-15</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M52" s="16" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>期限超過（2か月）</t>
         </is>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない。最も厳しい案Aでも第1回の期限は11月6日で、残りは1か月である</t>
+          <t>自立度Ⅲa・Ⅲbが受領資料になく、「自立度Ⅱ以上」の合計が出せない（見える化Ｂ7）。このため認知症高齢者数の見込みは下限（令和9年度335人）にとどまる。研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）。初期集中支援チームの令和6・7年度の実績も要る（見える化の直近値は令和5年度）　10月1日に認知症施策の体制と活動の図を作成（f47）。推進員1→4人、カフェ1か所で横ばい、初期集中支援チームの訪問実績0件</t>
         </is>
       </c>
     </row>
@@ -8519,59 +8519,59 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>認知症高齢者の分析</t>
+          <t>総合事業費の上限額の確認</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="I53" s="13" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="J53" s="13" t="n">
-        <v>100</v>
+        <v>37.8</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>-15</v>
+        <v>-12.8</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="14" t="inlineStr">
-        <is>
-          <t>期限超過（2か月）</t>
+        <v>3</v>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>自立度Ⅲa・Ⅲbが受領資料になく、「自立度Ⅱ以上」の合計が出せない（見える化Ｂ7）。このため認知症高齢者数の見込みは下限（令和9年度335人）にとどまる。研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）。初期集中支援チームの令和6・7年度の実績も要る（見える化の直近値は令和5年度）　10月1日に認知症施策の体制と活動の図を作成（f47）。推進員1→4人、カフェ1か所で横ばい、初期集中支援チームの訪問実績0件</t>
+          <t>町の「総合事業上限額算定の手引き（Excel）」（平成27年度〜令和6年度）と地域支援事業交付金事業実績報告書が要る。現に上限内に収まっているかを確かめられていない。上限を超えると超過分は町の一般財源となるため、サービスBを広げる場合（決定7）の判断に直結する</t>
         </is>
       </c>
     </row>
@@ -8583,22 +8583,22 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>総合事業費の上限額の確認</t>
+          <t>町の給付実績との突合</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -8608,34 +8608,34 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>-12.8</v>
+        <v>-6.7</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M54" s="16" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>町の「総合事業上限額算定の手引き（Excel）」（平成27年度〜令和6年度）と地域支援事業交付金事業実績報告書が要る。現に上限内に収まっているかを確かめられていない。上限を超えると超過分は町の一般財源となるため、サービスBを広げる場合（決定7）の判断に直結する</t>
+          <t>見える化システムの値との突合作業</t>
         </is>
       </c>
     </row>
@@ -8647,17 +8647,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>町の給付実績との突合</t>
+          <t>認定者数・認定率の分析</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -8667,30 +8667,30 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H55" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I55" s="13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>56.7</v>
+        <v>100</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>-6.7</v>
+        <v>0</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M55" s="17" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの値との突合作業</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -8711,17 +8711,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>認定者数・認定率の分析</t>
+          <t>集計結果・分析報告書の作成</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -8775,17 +8775,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>集計結果・分析報告書の作成</t>
+          <t>協議会資料（第9期評価・調査結果）の作成</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>開催日が未定。決まればすぐにお出しできる</t>
         </is>
       </c>
     </row>
@@ -8839,17 +8839,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>協議会資料（第9期評価・調査結果）の作成</t>
+          <t>算定シートの構築</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>開催日が未定。決まればすぐにお出しできる</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -8903,17 +8903,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>算定シートの構築</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M59" s="17" t="inlineStr">
         <is>
@@ -8972,12 +8972,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>第9期計画本文の確認</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>第9期計画本文の確認</t>
+          <t>人口・世帯の分析</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
@@ -9095,17 +9095,17 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>人口・世帯の分析</t>
+          <t>調査結果報告書の確認</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>―　9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。認知症の設問の項目名を1件訂正し、報告書そのものの食い違い3件を注記した</t>
         </is>
       </c>
     </row>
@@ -9159,17 +9159,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>調査結果報告書の確認</t>
+          <t>見える化システムへの入力作業</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>―　9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。認知症の設問の項目名を1件訂正し、報告書そのものの食い違い3件を注記した</t>
+          <t>9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。入力の前に直す設定が2件ある。①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の算式値（令和9年度6.107％・令和10年度5.548％・令和11年度4.945％）と突き合わせる</t>
         </is>
       </c>
     </row>
@@ -9223,17 +9223,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力作業</t>
+          <t>成果指標の目標値案の作成</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -9243,12 +9243,12 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>9月24日に、受領したワークシートを1行ずつ読んで入力値を確定した（見える化システム入力値一覧・入力の手順。11_見える化出力依頼）。入力の前に直す設定が2件ある。①1人1月あたり給付費の実績値が令和8年度になっている。令和8年度の列は1か月分で、人数・回数・日数の非ゼロ36件のうち31件（86.1％）が整数である（令和6年度は46件中5件、令和7年度は40件中8件で、いずれも12分の1単位の小数）。令和7年度に切り替える。②認定率の伸びが令和6年度→令和7年度になっている。見える化の認定者数は各年9月末の値で、令和7年度の865人は令和7年9月の断層の直後にあたる。令和6年度937人は国保連の令和6年10月審査分と一致し、令和7年度865人と令和8年度865人は同値で令和8年度に実績がないことを示す。計上方法の確認が取れるまでこの伸びは使えない。入力欄は、当方で用意できるものが28欄、町の資料が要るものが26欄。町の資料が要るのは一般介護予防事業5欄（計5,305千円）、包括的支援事業・任意事業8欄（計29,335千円）、審査支払手数料等2欄（計531千円）、準備基金、令和8年度の当初予算など。所得段階別加入割合13段階を入れると調整交付金見込交付割合が自動で出るため、当方の算式値（令和9年度6.107％・令和10年度5.548％・令和11年度4.945％）と突き合わせる</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -9287,17 +9287,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>成果指標の目標値案の作成</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -9307,24 +9307,24 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H65" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K65" s="13" t="n">
         <v>0</v>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -9356,12 +9356,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>原稿の確定</t>
         </is>
       </c>
     </row>
@@ -9415,17 +9415,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -9435,30 +9435,30 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I67" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M67" s="17" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>原稿の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>引継ぎ資料の整理</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>引継ぎ資料の整理</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -9671,17 +9671,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>サービス受給者数の分析</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>サービス受給者数の分析</t>
+          <t>サービス自給率の分析</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -9799,17 +9799,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>サービス自給率の分析</t>
+          <t>集計データの整理</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>集計データの整理</t>
+          <t>クロス集計の設計</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -9927,44 +9927,44 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>クロス集計の設計</t>
+          <t>骨子案の協議（協議会）</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I75" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J75" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K75" s="13" t="n">
         <v>0</v>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>協議会の開催回数・時期が未定（依頼票C4）</t>
         </is>
       </c>
     </row>
@@ -9991,44 +9991,44 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（協議会）</t>
+          <t>保険料算定のケース設定の確定</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K76" s="13" t="n">
         <v>0</v>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期が未定（依頼票C4）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10055,17 +10055,17 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>保険料算定のケース設定の確定</t>
+          <t>認知症施策推進基本計画の包含方針</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
         </is>
       </c>
     </row>
@@ -10124,39 +10124,39 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画の包含方針</t>
+          <t>素案の協議（協議会）</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H78" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I78" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K78" s="13" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等の意見をどう聴くか（同法13条3項→12条3項）。記述の追加では埋まらず策定過程に関わるため、協議会の委員構成を確認したうえで家族会・認知症カフェでの意見聴取の機会を設けるかを町と協議する。あわせて福島県の認知症施策推進計画の策定状況、町の意思決定（方式A／B）</t>
+          <t>協議会の開催時期</t>
         </is>
       </c>
     </row>
@@ -10183,17 +10183,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（協議会）</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>協議会の開催時期</t>
+          <t>P7の完了、開催日の確定</t>
         </is>
       </c>
     </row>
@@ -10252,12 +10252,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -10267,12 +10267,12 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -10316,39 +10316,39 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H81" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I81" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K81" s="13" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10380,39 +10380,39 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H82" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I82" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K82" s="13" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -10444,27 +10444,27 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -10503,22 +10503,22 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -10572,17 +10572,17 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>計画書の確定</t>
         </is>
       </c>
     </row>
@@ -10636,12 +10636,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>校了</t>
         </is>
       </c>
     </row>
@@ -10695,17 +10695,17 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>第1号被保険者の分析</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -10715,30 +10715,30 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H87" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I87" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" s="17" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10759,17 +10759,17 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者の分析</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -10779,24 +10779,24 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="H88" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I88" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K88" s="13" t="n">
         <v>0</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -10823,17 +10823,17 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -10843,24 +10843,24 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H89" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I89" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J89" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K89" s="13" t="n">
         <v>0</v>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10887,17 +10887,17 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -10907,24 +10907,24 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H90" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I90" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K90" s="13" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>骨子案の確定</t>
         </is>
       </c>
     </row>
@@ -10951,17 +10951,17 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>骨子案の確定</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -11015,17 +11015,17 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -11079,32 +11079,32 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -11143,44 +11143,44 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I94" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K94" s="13" t="n">
         <v>0</v>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>データCD-Rの作成</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -11227,24 +11227,24 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H95" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I95" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K95" s="13" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>各成果品の確定</t>
         </is>
       </c>
     </row>
@@ -11276,17 +11276,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>10-8</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>全成果品の完成</t>
         </is>
       </c>
     </row>
@@ -11335,50 +11335,50 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>10-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I97" s="13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M97" s="17" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
     </row>
@@ -11399,32 +11399,32 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>町データの受領</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -11433,16 +11433,16 @@
         </is>
       </c>
       <c r="I98" s="13" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>63.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数</t>
         </is>
       </c>
     </row>
@@ -11463,22 +11463,22 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>町データの受領</t>
+          <t>介護保険財政の分析</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -11506,7 +11506,7 @@
         <v>8.6</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M99" s="17" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
-          <t>残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数</t>
+          <t>令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る</t>
         </is>
       </c>
     </row>
@@ -11527,17 +11527,17 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>介護保険財政の分析</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H100" s="15" t="inlineStr">
@@ -11564,22 +11564,22 @@
         <v>80</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>8.6</v>
+        <v>16.8</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M100" s="17" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>4</v>
+      </c>
+      <c r="M100" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
@@ -11591,32 +11591,32 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>8-8</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>在宅医療・介護連携の目指すべき姿の設定</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
@@ -11625,16 +11625,16 @@
         </is>
       </c>
       <c r="I101" s="13" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>63.2</v>
+        <v>28.1</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M101" s="18" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
         </is>
       </c>
     </row>
@@ -11655,22 +11655,22 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>8-8</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携の目指すべき姿の設定</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
@@ -11689,16 +11689,16 @@
         </is>
       </c>
       <c r="I102" s="13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>28.1</v>
+        <v>37.8</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M102" s="18" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
+          <t>残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）</t>
         </is>
       </c>
     </row>
@@ -12167,17 +12167,17 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P11 品質・進捗管理</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>11-3</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>素案の構成・体裁の点検（他団体の第10期計画との対比）</t>
+          <t>図表の追加作成</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H110" s="15" t="inlineStr">
@@ -12201,16 +12201,16 @@
         </is>
       </c>
       <c r="I110" s="13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J110" s="13" t="n">
-        <v>37.8</v>
+        <v>28.1</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M110" s="18" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>残る未対応は、第5章の各施策の記載を5項目にそろえること、事業所調査（未実施。実施の可否を町と相談）、国の基本指針が示す確認すべき指標との対応表</t>
+          <t>残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である</t>
         </is>
       </c>
     </row>
@@ -12236,12 +12236,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>図表の追加作成</t>
+          <t>成果品の体裁の統一と機械点検</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
-          <t>残る2点はいずれも町データ待ち。地域ケア会議の開催回数・検討件数と、介護給付適正化の主要3事業の実施状況である</t>
+          <t>印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>P11 品質・進捗管理</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>成果品の体裁の統一と機械点検</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -12329,16 +12329,16 @@
         </is>
       </c>
       <c r="I112" s="13" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J112" s="13" t="n">
-        <v>28.1</v>
+        <v>42.8</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M112" s="18" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="N112" s="6" t="inlineStr">
         <is>
-          <t>印刷用の最終体裁（4色刷り・80頁）は組版工程（10-2）で別に点検する</t>
+          <t>9月24日に、受託者が算定すべき未確定箇所をすべて解消した。所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。あわせて数値の誤りを2件正した。①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、これは誤りで0.485が正しい（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
     </row>
@@ -12364,12 +12364,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-9</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>素案の構成・体裁の点検（他団体の第10期計画との対比）</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -12379,12 +12379,12 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H113" s="15" t="inlineStr">
@@ -12393,16 +12393,16 @@
         </is>
       </c>
       <c r="I113" s="13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>42.8</v>
+        <v>37.8</v>
       </c>
       <c r="K113" s="13" t="n">
         <v>52.2</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M113" s="18" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="N113" s="6" t="inlineStr">
         <is>
-          <t>9月24日に、受託者が算定すべき未確定箇所をすべて解消した。所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。あわせて数値の誤りを2件正した。①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、これは誤りで0.485が正しい（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>残る未対応は、第5章の各施策の記載を5項目にそろえること、事業所調査（未実施。実施の可否を町と相談）、国の基本指針が示す確認すべき指標との対応表</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
     <row r="123">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>高齢者計画　予定進捗率 55.3％　対　実績進捗率 69.8％　乖離 +14.5ポイント　／　おおむね予定どおり 46件／前倒し 21件／遅れ 5件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>高齢者計画　予定進捗率 55.1％　対　実績進捗率 70.2％　乖離 +15.0ポイント　／　おおむね予定どおり 46件／前倒し 22件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>サービス単価。当方は令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる</t>
+          <t>サービス単価。当方は令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額195円上がる</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>協議会・パブリックコメント・印刷の日程が引ける。令和9年2月下旬の校了は動かせないため、12月までに印刷を発注する必要がある</t>
+          <t>協議会・パブリックコメント・印刷の日程が引ける。令和9年2月下旬の校了は動かせない。逆算では発注は2月中旬まで待てるが、年度末は印刷が集中するため1月中に押さえる必要がある</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>サービス単価。当方は令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額211円上がる</t>
+          <t>サービス単価。当方は令和7年度で固定しているため、実績の趨勢（年率＋1.13％）で置くと標準給付費が3.43％・保険料が月額195円上がる</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12871,92 +12871,156 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>10-9</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>印刷の発注準備</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H121" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I121" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J121" s="13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K121" s="13" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
+        </is>
+      </c>
+      <c r="N121" s="6" t="inlineStr">
+        <is>
+          <t>町による用紙・校正の条件の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>高齢者</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
           <t>P7 推計・算定</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>7-6</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>保険料のケース別算定</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F122" s="5" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="H121" s="15" t="inlineStr">
+      <c r="H122" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="I121" s="13" t="n">
+      <c r="I122" s="13" t="n">
         <v>95</v>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J122" s="13" t="n">
         <v>6.7</v>
       </c>
-      <c r="K121" s="13" t="n">
+      <c r="K122" s="13" t="n">
         <v>88.3</v>
       </c>
-      <c r="L121" s="5" t="n">
+      <c r="L122" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M121" s="18" t="inlineStr">
+      <c r="M122" s="18" t="inlineStr">
         <is>
           <t>前倒し</t>
         </is>
       </c>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="N122" s="6" t="inlineStr">
         <is>
           <t>一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="19" t="inlineStr">
-        <is>
-          <t>高齢者計画　予定進捗率 55.1％　対　実績進捗率 70.2％　乖離 +15.0ポイント　／　おおむね予定どおり 46件／前倒し 22件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
+          <t>高齢者計画　予定進捗率 54.9％　対　実績進捗率 70.3％　乖離 +15.4ポイント　／　おおむね予定どおり 46件／前倒し 23件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
           <t>障がい計画　予定進捗率 50.6％　対　実績進捗率 33.1％　乖離 -17.5ポイント　／　おおむね予定どおり 27件／期限超過（1か月） 6件／遅れ 4件／前倒し 4件／期限超過（2か月） 3件</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>※ 予定進捗率＝予定開始の月初から予定完了の月末までを直線で見たとき、基準日に何％進んでいるはずかの値です。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>※ 差が±10ポイント以内なら「おおむね予定どおり」。月単位の予定を日割りした誤差の幅です。</t>
+          <t>※ 予定進捗率＝予定開始の月初から予定完了の月末までを直線で見たとき、基準日に何％進んでいるはずかの値です。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>※ 差が±10ポイント以内なら「おおむね予定どおり」。月単位の予定を日割りした誤差の幅です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t>※ 業務進捗管理表の 11_進捗の乖離 と同じ関数で計算しているため、両者がずれることはありません。</t>
         </is>
@@ -13317,7 +13381,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>年報 様式2 の実績で計算済み（報酬改定のない年でも年率＋1.09％、改定のあった令和6年度は＋1.25％）。単価を令和7年度で固定している当方の置き方は過小側であり、実績の趨勢で置くと保険料が月額211円上がる。保険料の決定（決定1）の判断材料になる</t>
+          <t>年報 様式2 の実績で計算済み（報酬改定のない年でも年率＋1.09％、改定のあった令和6年度は＋1.25％）。単価を令和7年度で固定している当方の置き方は過小側であり、実績の趨勢（連鎖ラスパイレス指数で年率＋1.13％）で置くと保険料が月額195円上がる。保険料の決定（決定1）の判断材料になる</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -13425,17 +13489,17 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13470,17 +13534,17 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13497,7 +13561,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>成果品⑤⑥の仕様（A4・4色刷り・計画書80頁50部／概要版8頁50部）は仕様書に確定している。12月までに発注しないと令和9年2月下旬の校了に間に合わない</t>
+          <t>成果品⑤⑥の仕様（A4・4色刷り・計画書80頁50部／概要版8頁50部）は仕様書に確定している。年度末は印刷が集中するため、1月中に業者を押さえる必要がある</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -13510,22 +13574,22 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-9／10-6</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13624,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>10月7日（水）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -13605,7 +13669,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>10月7日（水）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -13650,7 +13714,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>10月8日（木）</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -13695,7 +13759,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>10月8日（木）</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -13734,7 +13798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13786,7 +13850,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>10月2日（金）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
@@ -13794,32 +13858,32 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>工程変更協議資料の改訂（高齢者・障がい）</t>
+          <t>素案 第5章の各施策の記載を5項目にそろえる</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+        <v>4</v>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>8-9／8-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>10月2日（金）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -13827,12 +13891,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>要介護度の維持・改善率の図の作成</t>
+          <t>単価の置き方の感度分析の文書化</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -13845,14 +13909,14 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>11-2／11-3</t>
+          <t>7-6／7-7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>10月2日（金）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -13860,16 +13924,16 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>中長期（令和22年度）の給付費の見通し</t>
+          <t>見える化 医療・リハビリの出力依頼（絞り込み）</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
@@ -13878,54 +13942,64 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>8-9／7-4</t>
+          <t>2-10／8-8</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>10月2日（金）</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>── 10月2日（金） 計</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>成果品②（サービス見込量推計結果報告書）の仕上げ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>7-7</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>10月4日（日）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>図表番号一覧の作成</t>
+          <t>骨子案を素案の6章構成に合わせる（第4版）</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
@@ -13934,31 +14008,31 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>8-9／11-2</t>
+          <t>6-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>10月4日（日）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>介護保険制度改正の内容の節</t>
+          <t>印刷の仕様書と見積依頼の様式</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
@@ -13967,29 +14041,29 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>8-9</t>
+          <t>10-9／10-6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>10月4日（日）</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr"/>
       <c r="C8" s="20" t="inlineStr"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>── 10月4日（日） 計</t>
+          <t>── 10月5日（月） 計</t>
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>完了</t>
+        <v>4</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>残4.0h</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr"/>
@@ -13997,7 +14071,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -14005,12 +14079,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章の各施策の記載を5項目にそろえる</t>
+          <t>協議会 第2回の資料の骨格</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -14023,14 +14097,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>8-9／8-1</t>
+          <t>9-3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -14038,105 +14112,105 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>単価の置き方の感度分析の文書化</t>
+          <t>概要版（8頁）のページ割りと図の割付</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>7-6／7-7</t>
+          <t>10-5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>10月5日（月）</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>見える化 医療・リハビリの出力依頼（絞り込み）</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>2-10／8-8</t>
-        </is>
-      </c>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>10月6日（火）</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>── 10月6日（火） 計</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>残6.0h</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>10月5日（月）</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>── 10月5日（月） 計</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>残4.0h</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画の素案の改訂（第2版）</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>障がい 3-2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>成果品②（サービス見込量推計結果報告書）の仕上げ</t>
+          <t>一次資料との突合の対象を広げる</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -14145,286 +14219,42 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>骨子案を素案の6章構成に合わせる（第4版）</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>6-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>印刷の仕様書と見積依頼の様式</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>10-6</t>
-        </is>
-      </c>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>── 10月7日（水） 計</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>残8.0h</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>── 10月6日（火） 計</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>残8.0h</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>協議会 第2回の資料の骨格</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>9-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>概要版（8頁）のページ割りと図の割付</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>── 10月7日（水） 計</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>残6.0h</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>一次資料との突合の対象を広げる</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>── 10月8日（木） 計</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>残8.0h</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
@@ -13344,7 +13344,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>素案 第9版／構成の対比（△9件→○）</t>
+          <t>素案 第9版／構成の対比（△9件→○22件）</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -13357,14 +13357,14 @@
           <t>10月5日（月）</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13850,7 +13850,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章の各施策の記載を5項目にそろえる</t>
+          <t>協議会 第2回の資料の骨格</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13876,14 +13876,14 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>8-9／8-1</t>
+          <t>9-3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -13891,370 +13891,149 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>単価の置き方の感度分析の文書化</t>
+          <t>概要版（8頁）のページ割りと図の割付</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>7-6／7-7</t>
+          <t>10-5</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>10月5日（月）</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>見える化 医療・リハビリの出力依頼（絞り込み）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>2-10／8-8</t>
-        </is>
-      </c>
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>10月6日（火）</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr"/>
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>── 10月6日（火） 計</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>残6.0h</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>成果品②（サービス見込量推計結果報告書）の仕上げ</t>
+          <t>障がい計画の素案の改訂（第2版）</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+        <v>6</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>障がい 3-2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>骨子案を素案の6章構成に合わせる（第4版）</t>
+          <t>一次資料との突合の対象を広げる</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+        <v>2</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>11-1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>10月5日（月）</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>印刷の仕様書と見積依頼の様式</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>10-9／10-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>10月5日（月）</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>── 10月5日（月） 計</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>残4.0h</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr"/>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>── 10月7日（水） 計</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>残8.0h</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>協議会 第2回の資料の骨格</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>9-3</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>概要版（8頁）のページ割りと図の割付</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>── 10月6日（火） 計</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>残6.0h</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>一次資料との突合の対象を広げる</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>── 10月7日（水） 計</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>残8.0h</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261005.xlsx
@@ -10188,12 +10188,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -10252,39 +10252,39 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I80" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K80" s="13" t="n">
         <v>0</v>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10316,39 +10316,39 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H81" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I81" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="13" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -10380,27 +10380,27 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -10439,22 +10439,22 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -10508,17 +10508,17 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>計画書の確定</t>
         </is>
       </c>
     </row>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>校了</t>
         </is>
       </c>
     </row>
@@ -10631,17 +10631,17 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>第1号被保険者の分析</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H86" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I86" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10695,17 +10695,17 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者の分析</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -10715,24 +10715,24 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="H87" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I87" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K87" s="13" t="n">
         <v>0</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -10759,17 +10759,17 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -10779,24 +10779,24 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I88" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K88" s="13" t="n">
         <v>0</v>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -10823,17 +10823,17 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -10843,24 +10843,24 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H89" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I89" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="13" t="n">
         <v>0</v>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>骨子案の確定</t>
         </is>
       </c>
     </row>
@@ -10887,17 +10887,17 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>骨子案の確定</t>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -10951,17 +10951,17 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -11015,32 +11015,32 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -11079,32 +11079,32 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>データCD-Rの作成</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>各成果品の確定</t>
         </is>
       </c>
     </row>
@@ -11148,39 +11148,39 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-8</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H94" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I94" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="13" t="n">
         <v>0</v>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>全成果品の完成</t>
         </is>
       </c>
     </row>
@@ -11207,17 +11207,17 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -11227,30 +11227,30 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H95" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I95" s="13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M95" s="17" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
     </row>
@@ -11271,50 +11271,50 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>10-8</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>町データの受領</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I96" s="13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M96" s="17" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数</t>
         </is>
       </c>
     </row>
@@ -11335,17 +11335,17 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>介護保険財政の分析</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H97" s="15" t="inlineStr">
@@ -11369,16 +11369,16 @@
         </is>
       </c>
       <c r="I97" s="13" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>63.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M97" s="17" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る</t>
         </is>
       </c>
     </row>
@@ -11399,32 +11399,32 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>町データの受領</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -11436,22 +11436,22 @@
         <v>80</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>8.6</v>
+        <v>16.8</v>
       </c>
       <c r="L98" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M98" s="17" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+      <c r="M98" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
-          <t>残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）、総合事業上限額算定の手引き、地域支援事業交付金事業実績報告書、令和6年度のケアプラン点検の実施件数</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
@@ -11463,32 +11463,32 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>8-8</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>介護保険財政の分析</t>
+          <t>在宅医療・介護連携の目指すべき姿の設定</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H99" s="15" t="inlineStr">
@@ -11497,25 +11497,25 @@
         </is>
       </c>
       <c r="I99" s="13" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>71.40000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>8.6</v>
+        <v>16.9</v>
       </c>
       <c r="L99" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M99" s="17" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+      <c r="M99" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る</t>
+          <t>目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
         </is>
       </c>
     </row>
@@ -11527,17 +11527,17 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -11561,16 +11561,16 @@
         </is>
       </c>
       <c r="I100" s="13" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>63.2</v>
+        <v>37.8</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M100" s="18" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）</t>
         </is>
       </c>
     </row>
@@ -11591,17 +11591,17 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>8-8</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携の目指すべき姿の設定</t>
+          <t>認定者数の異常値の検証</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -11611,12 +11611,12 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
@@ -11625,16 +11625,16 @@
         </is>
       </c>
       <c r="I101" s="13" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>28.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>16.9</v>
+        <v>18.6</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M101" s="18" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
-          <t>目指すべき姿の内容の確定（決定11）。公立小野町地方綜合病院・田村郡医師会等との調整が要る。あわせて在宅医療・介護連携推進事業の実施状況（相談窓口の運営、多職種研修、情報共有ツール）</t>
+          <t>「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか</t>
         </is>
       </c>
     </row>
@@ -11660,12 +11660,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>総合事業の実施状況の分析</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
@@ -11689,16 +11689,16 @@
         </is>
       </c>
       <c r="I102" s="13" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>17.2</v>
+        <v>28.3</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" s="18" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）</t>
+          <t>ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る　10月1日に通いの場の図を作成（f48）。見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
         </is>
       </c>
     </row>
@@ -11719,22 +11719,22 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P10 完成・納品</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>認定者数の異常値の検証</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -11747,22 +11747,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H103" s="15" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H103" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I103" s="13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J103" s="13" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>18.6</v>
+        <v>28.6</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M103" s="18" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -11783,22 +11783,22 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況の分析</t>
+          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H104" s="15" t="inlineStr">
@@ -11817,13 +11817,13 @@
         </is>
       </c>
       <c r="I104" s="13" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>56.7</v>
+        <v>28.1</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>28.3</v>
+        <v>31.9</v>
       </c>
       <c r="L104" s="5" t="n">
         <v>3</v>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>ワークシートに載る実施状況調査の回答は、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408→24→150→24人と激しく振れている。時系列として使えないため、町の控え（平成29年度〜令和6年度）との突合が要る　10月1日に通いの場の図を作成（f48）。見える化は平成28年度以降0か所、調査では13.8％が年に数回以上参加。食い違いの解明は町の事業実績待ち</t>
+          <t>位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る</t>
         </is>
       </c>
     </row>
@@ -11847,22 +11847,22 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化計画の位置づけと主要3事業の定量目標</t>
+          <t>被保険者数・認定者数の推計</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H105" s="15" t="inlineStr">
@@ -11881,16 +11881,16 @@
         </is>
       </c>
       <c r="I105" s="13" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>28.1</v>
+        <v>56.7</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>31.9</v>
+        <v>33.3</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M105" s="18" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="N105" s="6" t="inlineStr">
         <is>
-          <t>位置づけの決定（決定9）と、ケアプラン点検の点検件数の目標（決定10）。あわせて、令和6年度のケアプラン点検の実施件数（0点の理由が件数の少なさか報告していないことかの特定）と、要介護認定の適正化の実施内容（認定調査の委託の有無と点検件数）が要る</t>
+          <t>認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
         </is>
       </c>
     </row>
@@ -11911,17 +11911,17 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>被保険者数・認定者数の推計</t>
+          <t>成果目標の達成状況の確定</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -11954,7 +11954,7 @@
         <v>33.3</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M106" s="18" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる。あわせて、認定率の分子に第2号被保険者の認定者を含むかを見える化の画面で確認する（確認事項No.125）</t>
+          <t>地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ</t>
         </is>
       </c>
     </row>
@@ -11975,17 +11975,17 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の確定</t>
+          <t>地域分析・検討シートの記入案の作成</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -12018,7 +12018,7 @@
         <v>33.3</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M107" s="18" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ</t>
+          <t>町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る</t>
         </is>
       </c>
     </row>
@@ -12039,32 +12039,32 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>地域分析・検討シートの記入案の作成</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H108" s="15" t="inlineStr">
@@ -12073,13 +12073,13 @@
         </is>
       </c>
       <c r="I108" s="13" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="L108" s="5" t="n">
         <v>2</v>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>町の確定稿への記入は町が行う。記入案のうち通いの場・総合事業に関する記述は2-6・2-12と同じデータ待ちで、町の事業実績が入ると書き換えが要る</t>
+          <t>開催日の確定（案Aなら11月27日が期限）</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>高齢者計画　予定進捗率 54.9％　対　実績進捗率 70.3％　乖離 +15.4ポイント　／　おおむね予定どおり 46件／前倒し 23件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>高齢者計画　予定進捗率 54.8％　対　実績進捗率 70.7％　乖離 +16.0ポイント　／　おおむね予定どおり 44件／前倒し 25件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -13624,17 +13624,17 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13664,22 +13664,22 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-4／10-5</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月5日（月）</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月5日（月）</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>10月7日（水）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>10月7日（水）</t>
+          <t>10月6日（火）</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -13798,7 +13798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13858,16 +13858,16 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>協議会 第2回の資料の骨格</t>
+          <t>障がい計画の素案の改訂（第2版）</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>障がい 3-2</t>
         </is>
       </c>
     </row>
@@ -13891,12 +13891,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>概要版（8頁）のページ割りと図の割付</t>
+          <t>一次資料との突合の対象を広げる</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>11-1</t>
         </is>
       </c>
     </row>
@@ -13927,113 +13927,24 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>残6.0h</t>
+          <t>残8.0h</t>
         </is>
       </c>
       <c r="G4" s="20" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>一次資料との突合の対象を広げる</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>11-1</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>10月7日（水）</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>── 10月7日（水） 計</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>残8.0h</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>※ 10月6日（火）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>
@@ -18086,13 +17997,13 @@
           <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107">
@@ -18124,13 +18035,13 @@
           <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
-      <c r="G107" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G107" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108">
@@ -18162,13 +18073,13 @@
           <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
-      <c r="G108" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
@@ -18200,13 +18111,13 @@
           <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
-      <c r="G109" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G109" s="15" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110">
